--- a/scripts/ArmorInfo/TLS_ITEM_VALUES.xlsx
+++ b/scripts/ArmorInfo/TLS_ITEM_VALUES.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2872" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2876" uniqueCount="379">
   <si>
     <t>Tag</t>
   </si>
@@ -471,426 +471,435 @@
     <t>MagicDamage</t>
   </si>
   <si>
+    <t>ArmorCleanse</t>
+  </si>
+  <si>
+    <t>22/30/38/46/54/62</t>
+  </si>
+  <si>
+    <t>10/14/18/22/26/30</t>
+  </si>
+  <si>
+    <t>13/18/23/29/34/39</t>
+  </si>
+  <si>
+    <t>ArmorRun</t>
+  </si>
+  <si>
+    <t>15/21/27/32/37/42</t>
+  </si>
+  <si>
+    <t>17/23/29/35/42/49</t>
+  </si>
+  <si>
+    <t>5/6/8/9/11/12</t>
+  </si>
+  <si>
+    <t>19/26/34/42/50/59</t>
+  </si>
+  <si>
+    <t>3/4/6/7/9/10</t>
+  </si>
+  <si>
+    <t>PropagationBouncesModifier</t>
+  </si>
+  <si>
+    <t>6/7/9/10/12/13</t>
+  </si>
+  <si>
+    <t>21/29/38/46/55/63</t>
+  </si>
+  <si>
+    <t>16/20/24/28/32/36</t>
+  </si>
+  <si>
+    <t>11/15/19/24/28/32</t>
+  </si>
+  <si>
+    <t>24/33/43/54/65/77</t>
+  </si>
+  <si>
+    <t>18/23/29/36/44/53</t>
+  </si>
+  <si>
+    <t>Watchout</t>
+  </si>
+  <si>
+    <t>-10/-9/-8/-7/-6/-5</t>
+  </si>
+  <si>
+    <t>4/5/6/7/8/9</t>
+  </si>
+  <si>
+    <t>-5/-5/-5/-5/-5/-5</t>
+  </si>
+  <si>
+    <t>Leather Cap</t>
+  </si>
+  <si>
+    <t>12/17/26/40/60/87</t>
+  </si>
+  <si>
+    <t>Mail Coif</t>
+  </si>
+  <si>
+    <t>3/4/5/7/9/11</t>
+  </si>
+  <si>
+    <t>Nasal Helmet</t>
+  </si>
+  <si>
+    <t>Kettle Hat</t>
+  </si>
+  <si>
+    <t>2/3/4/6/8/10</t>
+  </si>
+  <si>
+    <t>Full Helm</t>
+  </si>
+  <si>
+    <t>5/6/7/9/11/13</t>
+  </si>
+  <si>
+    <t>10/14/22/28/34/40</t>
+  </si>
+  <si>
+    <t>Winged Helm</t>
+  </si>
+  <si>
+    <t>1/1/1/1/1/2</t>
+  </si>
+  <si>
+    <t>Magic Hat</t>
+  </si>
+  <si>
+    <t>16/22/32/47/68/97</t>
+  </si>
+  <si>
+    <t>Cursed Crown</t>
+  </si>
+  <si>
+    <t>-10/-10/-10/-10/-10/-10</t>
+  </si>
+  <si>
+    <t>Priest Helm</t>
+  </si>
+  <si>
+    <t>Eye Patch</t>
+  </si>
+  <si>
+    <t>Ronin Scarf</t>
+  </si>
+  <si>
+    <t>Rogue Hood</t>
+  </si>
+  <si>
+    <t>Goat Head</t>
+  </si>
+  <si>
+    <t>Stag Helm</t>
+  </si>
+  <si>
+    <t>2/4/6/8/10/12</t>
+  </si>
+  <si>
+    <t>Lone Wolf Helm</t>
+  </si>
+  <si>
+    <t>20/25/30/35/40/45</t>
+  </si>
+  <si>
+    <t>Spiked Helm</t>
+  </si>
+  <si>
+    <t>3/5/7/9/11/12</t>
+  </si>
+  <si>
+    <t>Devil Helm</t>
+  </si>
+  <si>
+    <t>Brute Helm</t>
+  </si>
+  <si>
+    <t>24/34/44/54/64/74</t>
+  </si>
+  <si>
+    <t>Steel Helm</t>
+  </si>
+  <si>
+    <t>Cultist Hood</t>
+  </si>
+  <si>
+    <t>Raven Queen's Beak</t>
+  </si>
+  <si>
+    <t>Prophet Veil</t>
+  </si>
+  <si>
+    <t>Steppe Hunter Hood</t>
+  </si>
+  <si>
+    <t>Inquisitor Hat</t>
+  </si>
+  <si>
+    <t>Frost Mage Headpiece</t>
+  </si>
+  <si>
+    <t>2/2/3/3/4/4</t>
+  </si>
+  <si>
+    <t>2/3/4/5/6/7</t>
+  </si>
+  <si>
+    <t>15/22/29/36/43/50</t>
+  </si>
+  <si>
+    <t>11/16/21/25/30/35</t>
+  </si>
+  <si>
+    <t>15/21/27/33/37/45</t>
+  </si>
+  <si>
+    <t>Culist Hood</t>
+  </si>
+  <si>
+    <t>Worn Pants</t>
+  </si>
+  <si>
+    <t>12/15/21/30/42/57</t>
+  </si>
+  <si>
+    <t>Linen Pants</t>
+  </si>
+  <si>
+    <t>Woolen Pants</t>
+  </si>
+  <si>
+    <t>Fur Pants</t>
+  </si>
+  <si>
+    <t>3/5/7/8/9/10</t>
+  </si>
+  <si>
+    <t>5/8/11/14/17/20</t>
+  </si>
+  <si>
+    <t>Leather Pants</t>
+  </si>
+  <si>
+    <t>Silk Pants</t>
+  </si>
+  <si>
+    <t>Worn Greaves</t>
+  </si>
+  <si>
+    <t>Greaves</t>
+  </si>
+  <si>
+    <t>Reinforced Greaves</t>
+  </si>
+  <si>
+    <t>Heavy Greaves</t>
+  </si>
+  <si>
+    <t>-4/-4/-4/-5/-5/-5</t>
+  </si>
+  <si>
+    <t>Warlock Greaves</t>
+  </si>
+  <si>
+    <t>Paladin Greaves</t>
+  </si>
+  <si>
+    <t>Cursed Pants</t>
+  </si>
+  <si>
+    <t>16/19/25/34/46/61</t>
+  </si>
+  <si>
+    <t>Stag Greaves</t>
+  </si>
+  <si>
+    <t>Brute Greaves</t>
+  </si>
+  <si>
+    <t>-6/-6/-6/-7/-7/-7</t>
+  </si>
+  <si>
+    <t>Lone Wolf Greaves</t>
+  </si>
+  <si>
+    <t>Magic Boots</t>
+  </si>
+  <si>
+    <t>2/4/6/8/9/10</t>
+  </si>
+  <si>
+    <t>Spiked Greaves</t>
+  </si>
+  <si>
+    <t>Rogue Pants</t>
+  </si>
+  <si>
+    <t>Devil Greaves</t>
+  </si>
+  <si>
+    <t>-20/-20/-20/-20/-20/-20</t>
+  </si>
+  <si>
+    <t>Priest Boots</t>
+  </si>
+  <si>
+    <t>Gladiator Greaves</t>
+  </si>
+  <si>
+    <t>Commander Boots</t>
+  </si>
+  <si>
+    <t>Steel Greaves</t>
+  </si>
+  <si>
+    <t>Ronin Boots</t>
+  </si>
+  <si>
+    <t>Wildling Pants</t>
+  </si>
+  <si>
+    <t>Noble Pants</t>
+  </si>
+  <si>
+    <t>Slayer Pants</t>
+  </si>
+  <si>
+    <t>Warrior Greaves</t>
+  </si>
+  <si>
+    <t>Cultist Pants</t>
+  </si>
+  <si>
+    <t>25/30/35/40/45/50</t>
+  </si>
+  <si>
+    <t>-15/-15/-15/-15/-15/-15</t>
+  </si>
+  <si>
+    <t>Raven Queen's Talons</t>
+  </si>
+  <si>
+    <t>Prophet Loincloth</t>
+  </si>
+  <si>
+    <t>Steppe Hunter Pants</t>
+  </si>
+  <si>
+    <t>Inquisitor Pants</t>
+  </si>
+  <si>
+    <t>Frost Mage Pants</t>
+  </si>
+  <si>
+    <t>4/6/8/9/11/13</t>
+  </si>
+  <si>
+    <t>8/12/16/20/24/28</t>
+  </si>
+  <si>
+    <t>10/13/16/19/22/25</t>
+  </si>
+  <si>
+    <t>12/16/21/25/30/34</t>
+  </si>
+  <si>
+    <t>11/14/18/21/25/28</t>
+  </si>
+  <si>
+    <t>13/18/23/28/33/38</t>
+  </si>
+  <si>
+    <t>12/17/21/26/30/35</t>
+  </si>
+  <si>
+    <t>20/29/38/47/56/65</t>
+  </si>
+  <si>
+    <t>16/21/27/32/38/43</t>
+  </si>
+  <si>
+    <t>11/15/19/23/27/31</t>
+  </si>
+  <si>
+    <t>10/14/17/21/24/28</t>
+  </si>
+  <si>
+    <t>-8/-10/-12/-13/-15/-16</t>
+  </si>
+  <si>
+    <t>4/6/8/11/13/15</t>
+  </si>
+  <si>
+    <t>3/3/4/4/5/5</t>
+  </si>
+  <si>
+    <t>25/35/45/55/65/75</t>
+  </si>
+  <si>
+    <t>Swift Boots</t>
+  </si>
+  <si>
+    <t>Armored Boots</t>
+  </si>
+  <si>
+    <t>15/19/27/32/39/45</t>
+  </si>
+  <si>
+    <t>Holy Ring</t>
+  </si>
+  <si>
     <t>Cleanse</t>
   </si>
   <si>
-    <t>22/30/38/46/54/62</t>
-  </si>
-  <si>
-    <t>10/14/18/22/26/30</t>
-  </si>
-  <si>
-    <t>13/18/23/29/34/39</t>
+    <t>7/9/11/13/15/17</t>
+  </si>
+  <si>
+    <t>-10/-13/-16/-19/-22/-25</t>
+  </si>
+  <si>
+    <t>Sturdy Boots</t>
+  </si>
+  <si>
+    <t>Spiked Boots</t>
+  </si>
+  <si>
+    <t>-2/-2/-2/-2/-2/-2</t>
+  </si>
+  <si>
+    <t>Hunter Cape</t>
+  </si>
+  <si>
+    <t>Mana Ring</t>
+  </si>
+  <si>
+    <t>Troll Blood Amulet</t>
+  </si>
+  <si>
+    <t>Stingy Turtle Charm</t>
+  </si>
+  <si>
+    <t>Attack Turtle Charm</t>
+  </si>
+  <si>
+    <t>-10/-10/-10/-10/-10/-15</t>
+  </si>
+  <si>
+    <t>25/25/25/25/25/30</t>
+  </si>
+  <si>
+    <t>Mystic Elven Boots</t>
   </si>
   <si>
     <t>Run</t>
   </si>
   <si>
-    <t>15/21/27/32/37/42</t>
-  </si>
-  <si>
-    <t>17/23/29/35/42/49</t>
-  </si>
-  <si>
-    <t>5/6/8/9/11/12</t>
-  </si>
-  <si>
-    <t>19/26/34/42/50/59</t>
-  </si>
-  <si>
-    <t>3/4/6/7/9/10</t>
-  </si>
-  <si>
-    <t>PropagationBouncesModifier</t>
-  </si>
-  <si>
-    <t>6/7/9/10/12/13</t>
-  </si>
-  <si>
-    <t>21/29/38/46/55/63</t>
-  </si>
-  <si>
-    <t>16/20/24/28/32/36</t>
-  </si>
-  <si>
-    <t>11/15/19/24/28/32</t>
-  </si>
-  <si>
-    <t>24/33/43/54/65/77</t>
-  </si>
-  <si>
-    <t>18/23/29/36/44/53</t>
-  </si>
-  <si>
-    <t>Watchout</t>
-  </si>
-  <si>
-    <t>-10/-10/-10/-10/-10/-10</t>
-  </si>
-  <si>
-    <t>4/5/6/7/8/9</t>
-  </si>
-  <si>
-    <t>-5/-5/-5/-5/-5/-5</t>
-  </si>
-  <si>
-    <t>Leather Cap</t>
-  </si>
-  <si>
-    <t>12/17/26/40/60/87</t>
-  </si>
-  <si>
-    <t>Mail Coif</t>
-  </si>
-  <si>
-    <t>3/4/5/7/9/11</t>
-  </si>
-  <si>
-    <t>Nasal Helmet</t>
-  </si>
-  <si>
-    <t>Kettle Hat</t>
-  </si>
-  <si>
-    <t>2/3/4/6/8/10</t>
-  </si>
-  <si>
-    <t>Full Helm</t>
-  </si>
-  <si>
-    <t>5/6/7/9/11/13</t>
-  </si>
-  <si>
-    <t>10/14/22/28/34/40</t>
-  </si>
-  <si>
-    <t>Winged Helm</t>
-  </si>
-  <si>
-    <t>1/1/1/1/1/2</t>
-  </si>
-  <si>
-    <t>Magic Hat</t>
-  </si>
-  <si>
-    <t>16/22/32/47/68/97</t>
-  </si>
-  <si>
-    <t>Cursed Crown</t>
-  </si>
-  <si>
-    <t>Priest Helm</t>
-  </si>
-  <si>
-    <t>Eye Patch</t>
-  </si>
-  <si>
-    <t>Ronin Scarf</t>
-  </si>
-  <si>
-    <t>Rogue Hood</t>
-  </si>
-  <si>
-    <t>Goat Head</t>
-  </si>
-  <si>
-    <t>Stag Helm</t>
-  </si>
-  <si>
-    <t>2/4/6/8/10/12</t>
-  </si>
-  <si>
-    <t>Lone Wolf Helm</t>
-  </si>
-  <si>
-    <t>20/25/30/35/40/45</t>
-  </si>
-  <si>
-    <t>Spiked Helm</t>
-  </si>
-  <si>
-    <t>3/5/7/9/11/12</t>
-  </si>
-  <si>
-    <t>Devil Helm</t>
-  </si>
-  <si>
-    <t>Brute Helm</t>
-  </si>
-  <si>
-    <t>24/34/44/54/64/74</t>
-  </si>
-  <si>
-    <t>Steel Helm</t>
-  </si>
-  <si>
-    <t>Cultist Hood</t>
-  </si>
-  <si>
-    <t>Raven Queen's Beak</t>
-  </si>
-  <si>
-    <t>Prophet Veil</t>
-  </si>
-  <si>
-    <t>Steppe Hunter Hood</t>
-  </si>
-  <si>
-    <t>Inquisitor Hat</t>
-  </si>
-  <si>
-    <t>Frost Mage Headpiece</t>
-  </si>
-  <si>
-    <t>2/2/3/3/4/4</t>
-  </si>
-  <si>
-    <t>2/3/4/5/6/7</t>
-  </si>
-  <si>
-    <t>15/22/29/36/43/50</t>
-  </si>
-  <si>
-    <t>11/16/21/25/30/35</t>
-  </si>
-  <si>
-    <t>15/21/27/33/37/45</t>
-  </si>
-  <si>
-    <t>Culist Hood</t>
-  </si>
-  <si>
-    <t>Worn Pants</t>
-  </si>
-  <si>
-    <t>12/15/21/30/42/57</t>
-  </si>
-  <si>
-    <t>Linen Pants</t>
-  </si>
-  <si>
-    <t>Woolen Pants</t>
-  </si>
-  <si>
-    <t>Fur Pants</t>
-  </si>
-  <si>
-    <t>3/5/7/8/9/10</t>
-  </si>
-  <si>
-    <t>5/8/11/14/17/20</t>
-  </si>
-  <si>
-    <t>Leather Pants</t>
-  </si>
-  <si>
-    <t>Silk Pants</t>
-  </si>
-  <si>
-    <t>Worn Greaves</t>
-  </si>
-  <si>
-    <t>Greaves</t>
-  </si>
-  <si>
-    <t>Reinforced Greaves</t>
-  </si>
-  <si>
-    <t>Heavy Greaves</t>
-  </si>
-  <si>
-    <t>-4/-4/-4/-5/-5/-5</t>
-  </si>
-  <si>
-    <t>Warlock Greaves</t>
-  </si>
-  <si>
-    <t>Paladin Greaves</t>
-  </si>
-  <si>
-    <t>Cursed Pants</t>
-  </si>
-  <si>
-    <t>16/19/25/34/46/61</t>
-  </si>
-  <si>
-    <t>Stag Greaves</t>
-  </si>
-  <si>
-    <t>Brute Greaves</t>
-  </si>
-  <si>
-    <t>-6/-6/-6/-7/-7/-7</t>
-  </si>
-  <si>
-    <t>Lone Wolf Greaves</t>
-  </si>
-  <si>
-    <t>Magic Boots</t>
-  </si>
-  <si>
-    <t>2/4/6/8/9/10</t>
-  </si>
-  <si>
-    <t>Spiked Greaves</t>
-  </si>
-  <si>
-    <t>Rogue Pants</t>
-  </si>
-  <si>
-    <t>Devil Greaves</t>
-  </si>
-  <si>
-    <t>-20/-20/-20/-20/-20/-20</t>
-  </si>
-  <si>
-    <t>Priest Boots</t>
-  </si>
-  <si>
-    <t>Gladiator Greaves</t>
-  </si>
-  <si>
-    <t>Commander Boots</t>
-  </si>
-  <si>
-    <t>Steel Greaves</t>
-  </si>
-  <si>
-    <t>Ronin Boots</t>
-  </si>
-  <si>
-    <t>Wildling Pants</t>
-  </si>
-  <si>
-    <t>Noble Pants</t>
-  </si>
-  <si>
-    <t>Slayer Pants</t>
-  </si>
-  <si>
-    <t>Warrior Greaves</t>
-  </si>
-  <si>
-    <t>Cultist Pants</t>
-  </si>
-  <si>
-    <t>25/30/35/40/45/50</t>
-  </si>
-  <si>
-    <t>-15/-15/-15/-15/-15/-15</t>
-  </si>
-  <si>
-    <t>Raven Queen's Talons</t>
-  </si>
-  <si>
-    <t>Prophet Loincloth</t>
-  </si>
-  <si>
-    <t>Steppe Hunter Pants</t>
-  </si>
-  <si>
-    <t>Inquisitor Pants</t>
-  </si>
-  <si>
-    <t>Frost Mage Pants</t>
-  </si>
-  <si>
-    <t>4/6/8/9/11/13</t>
-  </si>
-  <si>
-    <t>8/12/16/20/24/28</t>
-  </si>
-  <si>
-    <t>10/13/16/19/22/25</t>
-  </si>
-  <si>
-    <t>12/16/21/25/30/34</t>
-  </si>
-  <si>
-    <t>11/14/18/21/25/28</t>
-  </si>
-  <si>
-    <t>13/18/23/28/33/38</t>
-  </si>
-  <si>
-    <t>12/17/21/26/30/35</t>
-  </si>
-  <si>
-    <t>20/29/38/47/56/65</t>
-  </si>
-  <si>
-    <t>16/21/27/32/38/43</t>
-  </si>
-  <si>
-    <t>11/15/19/23/27/31</t>
-  </si>
-  <si>
-    <t>10/14/17/21/24/28</t>
-  </si>
-  <si>
-    <t>4/6/8/11/13/15</t>
-  </si>
-  <si>
-    <t>-5/-6/-7/-8/-9/-10</t>
-  </si>
-  <si>
-    <t>3/3/4/4/5/5</t>
-  </si>
-  <si>
-    <t>25/35/45/55/65/75</t>
-  </si>
-  <si>
-    <t>Swift Boots</t>
-  </si>
-  <si>
-    <t>Armored Boots</t>
-  </si>
-  <si>
-    <t>15/19/27/32/39/45</t>
-  </si>
-  <si>
-    <t>Holy Ring</t>
-  </si>
-  <si>
-    <t>7/9/11/13/15/17</t>
-  </si>
-  <si>
-    <t>-10/-13/-16/-19/-22/-25</t>
-  </si>
-  <si>
-    <t>Sturdy Boots</t>
-  </si>
-  <si>
-    <t>Spiked Boots</t>
-  </si>
-  <si>
-    <t>-2/-2/-2/-2/-2/-2</t>
-  </si>
-  <si>
-    <t>Hunter Cape</t>
-  </si>
-  <si>
-    <t>Mana Ring</t>
-  </si>
-  <si>
-    <t>Troll Blood Amulet</t>
-  </si>
-  <si>
-    <t>Stingy Turtle Charm</t>
-  </si>
-  <si>
-    <t>Attack Turtle Charm</t>
-  </si>
-  <si>
-    <t>-10/-10/-10/-10/-10/-15</t>
-  </si>
-  <si>
-    <t>25/25/25/25/25/30</t>
-  </si>
-  <si>
-    <t>Mystic Elven Boots</t>
-  </si>
-  <si>
     <t>Cracked Crystal</t>
   </si>
   <si>
@@ -931,9 +940,6 @@
   </si>
   <si>
     <t>Concentration</t>
-  </si>
-  <si>
-    <t>-10/-9/-8/-7/-6/-5</t>
   </si>
   <si>
     <t>10/10/10/10/10/10</t>
@@ -1159,7 +1165,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1172,6 +1178,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="12.0"/>
       <color theme="1"/>
       <name val="Roboto"/>
@@ -1179,6 +1190,11 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF000000"/>
+      <name val="Roboto"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1333,7 +1349,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1344,46 +1360,61 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="2" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="3" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="5" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="5" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="6" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="7" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="5" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="8" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="8" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="9" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="9" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="5" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -5168,16 +5199,12 @@
       <c r="G36" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="H36" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>65</v>
-      </c>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
       <c r="J36" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K36" s="2" t="s">
+      <c r="K36" s="3" t="s">
         <v>168</v>
       </c>
       <c r="L36" s="2" t="s">
@@ -5968,7 +5995,7 @@
         <v>120</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>98</v>
@@ -5985,7 +6012,7 @@
         <v>96</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>102</v>
@@ -6020,7 +6047,7 @@
         <v>96</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>102</v>
@@ -6043,7 +6070,7 @@
         <v>96</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>102</v>
@@ -6072,7 +6099,7 @@
         <v>96</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>102</v>
@@ -6101,7 +6128,7 @@
         <v>96</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>102</v>
@@ -6136,7 +6163,7 @@
         <v>96</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>102</v>
@@ -6148,7 +6175,7 @@
         <v>19</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>60</v>
@@ -6165,7 +6192,7 @@
         <v>96</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>102</v>
@@ -6177,7 +6204,7 @@
         <v>63</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>72</v>
@@ -6194,7 +6221,7 @@
         <v>96</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>102</v>
@@ -6224,7 +6251,7 @@
         <v>51</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M17" s="2" t="s">
         <v>184</v>
@@ -6235,7 +6262,7 @@
         <v>96</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>102</v>
@@ -6276,13 +6303,13 @@
         <v>96</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>44</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>81</v>
@@ -6305,7 +6332,7 @@
         <v>96</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>102</v>
@@ -6340,7 +6367,7 @@
         <v>96</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>102</v>
@@ -6369,7 +6396,7 @@
         <v>96</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>102</v>
@@ -6398,7 +6425,7 @@
         <v>96</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>102</v>
@@ -6410,7 +6437,7 @@
         <v>19</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>72</v>
@@ -6433,7 +6460,7 @@
         <v>96</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>102</v>
@@ -6474,7 +6501,7 @@
         <v>96</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>102</v>
@@ -6498,7 +6525,7 @@
         <v>51</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>184</v>
@@ -6509,13 +6536,13 @@
         <v>96</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>44</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>81</v>
@@ -6555,984 +6582,984 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="12" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="8" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="5" ht="22.5" customHeight="1">
+      <c r="A5" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="12" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="6" ht="22.5" customHeight="1">
+      <c r="A6" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="8" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="7" ht="22.5" customHeight="1">
+      <c r="A7" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="12" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="8" ht="22.5" customHeight="1">
+      <c r="A8" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="8" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="9" ht="22.5" customHeight="1">
+      <c r="A9" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="12" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="10" ht="22.5" customHeight="1">
+      <c r="A10" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="8" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="11" ht="22.5" customHeight="1">
+      <c r="A11" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="12" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="12" ht="22.5" customHeight="1">
+      <c r="A12" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="8" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="13" ht="22.5" customHeight="1">
+      <c r="A13" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="12" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="14" ht="22.5" customHeight="1">
+      <c r="A14" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="15" ht="22.5" customHeight="1">
+      <c r="A15" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="12" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="16" ht="22.5" customHeight="1">
+      <c r="A16" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="8" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="17" ht="22.5" customHeight="1">
+      <c r="A17" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="12" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="18" ht="22.5" customHeight="1">
+      <c r="A18" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="8" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="19" ht="22.5" customHeight="1">
+      <c r="A19" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="12" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="20" ht="22.5" customHeight="1">
+      <c r="A20" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="8" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="21" ht="22.5" customHeight="1">
+      <c r="A21" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="12" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="22" ht="22.5" customHeight="1">
+      <c r="A22" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
+      <c r="O22" s="8" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="23" ht="22.5" customHeight="1">
+      <c r="A23" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="12" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="24" ht="22.5" customHeight="1">
+      <c r="A24" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+      <c r="O24" s="8" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="25" ht="22.5" customHeight="1">
+      <c r="A25" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="12" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="26" ht="22.5" customHeight="1">
+      <c r="A26" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="7" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="E3" s="9" t="s">
+      <c r="C26" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E26" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="J4" s="5" t="s">
+      <c r="F26" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="7" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="7" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="D7" s="9" t="s">
+      <c r="G26" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="H26" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="I26" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="J26" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="11" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="D8" s="5" t="s">
+      <c r="K26" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="L26" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="7" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="7" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="7" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="11" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="7" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="15" ht="22.5" customHeight="1">
-      <c r="A15" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="11" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="16" ht="22.5" customHeight="1">
-      <c r="A16" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="7" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="17" ht="22.5" customHeight="1">
-      <c r="A17" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-      <c r="O17" s="11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="18" ht="22.5" customHeight="1">
-      <c r="A18" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="7" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="19" ht="22.5" customHeight="1">
-      <c r="A19" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
-      <c r="O19" s="11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="20" ht="22.5" customHeight="1">
-      <c r="A20" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="6"/>
-      <c r="O20" s="7" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="21" ht="22.5" customHeight="1">
-      <c r="A21" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
-      <c r="O21" s="11" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="22" ht="22.5" customHeight="1">
-      <c r="A22" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="L22" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
-      <c r="O22" s="7" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="23" ht="22.5" customHeight="1">
-      <c r="A23" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="K23" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="L23" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
-      <c r="O23" s="11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="24" ht="22.5" customHeight="1">
-      <c r="A24" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="I24" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="6"/>
-      <c r="O24" s="7" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="25" ht="22.5" customHeight="1">
-      <c r="A25" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="J25" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="10"/>
-      <c r="O25" s="11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="26" ht="22.5" customHeight="1">
-      <c r="A26" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="G26" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="H26" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="I26" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="J26" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="K26" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="L26" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="M26" s="14"/>
-      <c r="N26" s="14"/>
-      <c r="O26" s="15" t="s">
+      <c r="M26" s="16"/>
+      <c r="N26" s="16"/>
+      <c r="O26" s="17" t="s">
         <v>184</v>
       </c>
     </row>
@@ -7555,1260 +7582,1260 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="K1" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="L1" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="M1" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="N1" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="O1" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="16" t="s">
+      <c r="P1" s="18" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="16" t="s">
+      <c r="B2" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="P2" s="16" t="s">
-        <v>214</v>
+      <c r="P2" s="18" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="18" t="s">
+        <v>216</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="P3" s="18" t="s">
         <v>215</v>
       </c>
-      <c r="D3" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="16" t="s">
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F4" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="P4" s="18" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="P5" s="18" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="P6" s="18" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="H7" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="I7" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="P7" s="18" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="H8" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="J8" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="K8" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="P8" s="18" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="H9" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="I9" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="J9" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="K9" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P9" s="18" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="I10" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="J10" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="K10" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="P10" s="18" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="I11" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="J11" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="K11" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="P11" s="18" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="G12" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="H12" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="I12" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="J12" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="K12" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P12" s="18" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="G13" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="J13" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="K13" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="L13" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="M13" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="P13" s="18" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="I14" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="P14" s="18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="D15" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="E15" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="F15" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G15" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="I15" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="P15" s="18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="J16" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="K16" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="P16" s="18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="H17" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="I17" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="J17" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="K17" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="P3" s="16" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>216</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="16" t="s">
+      <c r="P17" s="18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F18" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="G18" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="H18" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="I18" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="J18" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="K18" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="P18" s="18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="G19" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="H19" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="J19" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="K19" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="L19" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="M19" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="P19" s="18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>239</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="G20" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="H20" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="I20" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="J20" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="K20" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="P20" s="18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="G21" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="H21" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="I21" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="J21" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K21" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="L21" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="M21" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="N21" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="O21" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="P21" s="18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G22" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="H22" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="I22" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="P22" s="18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G23" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="H23" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="I23" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="J23" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="K23" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="P23" s="18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>244</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G24" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="H24" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="I24" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="J24" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="K24" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="L24" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="M24" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="P24" s="18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G25" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="H25" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="I25" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="J25" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="K25" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="L25" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="M25" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="P25" s="18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="F26" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="G26" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="H26" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="I26" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="K26" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="P26" s="18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="F27" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G27" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="H27" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="I27" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="P27" s="18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="H28" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="I28" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="P28" s="18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="F29" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G29" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="H29" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="J29" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="K29" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="P29" s="18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F30" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="G30" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="H30" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="I30" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="J30" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="K30" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="P30" s="18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="F31" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="G31" s="18" t="s">
+        <v>252</v>
+      </c>
+      <c r="H31" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="I31" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="J31" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="K31" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="P31" s="18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="F32" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="G32" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="H32" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="I32" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="J32" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="K32" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="P32" s="18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>255</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="F33" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G33" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="H33" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="I33" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="H4" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="P4" s="16" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" s="16" t="s">
+      <c r="J33" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="K33" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P33" s="18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>256</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="F34" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H34" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="I34" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="J34" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="K34" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="L34" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="I5" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="P5" s="16" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="H6" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="P6" s="16" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="H7" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="I7" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="P7" s="16" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>222</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="16" t="s">
+      <c r="M34" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="P34" s="18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>257</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="F35" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G35" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="H8" s="16" t="s">
+      <c r="H35" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="I8" s="16" t="s">
+      <c r="I35" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="J8" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="K8" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="P8" s="16" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>223</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="H9" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="I9" s="16" t="s">
+      <c r="J35" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="K35" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="J9" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="K9" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="P9" s="16" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G10" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="H10" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="I10" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="J10" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="K10" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="P10" s="16" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" s="16" t="s">
+      <c r="P35" s="18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>258</v>
+      </c>
+      <c r="D36" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E36" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="F36" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="G36" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="H11" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="I11" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="J11" s="16" t="s">
+      <c r="H36" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="I36" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="J36" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="K36" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="L36" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="M36" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="N36" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="K11" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="P11" s="16" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="16" t="s">
+      <c r="O36" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="D12" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="F12" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="G12" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="H12" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="I12" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="J12" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="K12" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="P12" s="16" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="F13" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="G13" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="H13" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="I13" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="J13" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="K13" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="L13" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="M13" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="P13" s="16" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G14" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="H14" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="I14" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="P14" s="16" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B15" s="16" t="s">
+      <c r="P36" s="18" t="s">
         <v>231</v>
-      </c>
-      <c r="D15" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="E15" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="F15" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G15" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="H15" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="I15" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="P15" s="16" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>232</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="F16" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="G16" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="H16" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="I16" s="16" t="s">
-        <v>233</v>
-      </c>
-      <c r="J16" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="K16" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="P16" s="16" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>234</v>
-      </c>
-      <c r="D17" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="F17" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G17" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="H17" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="I17" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="J17" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="K17" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="P17" s="16" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>235</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="F18" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="G18" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="H18" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="I18" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="J18" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="K18" s="16" t="s">
-        <v>236</v>
-      </c>
-      <c r="P18" s="16" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>237</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="F19" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="G19" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="H19" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="I19" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="J19" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="K19" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="L19" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="M19" s="16" t="s">
-        <v>236</v>
-      </c>
-      <c r="P19" s="16" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>238</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="F20" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="G20" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="H20" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="I20" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="J20" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="K20" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="P20" s="16" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>239</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="F21" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="G21" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="H21" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="I21" s="16" t="s">
-        <v>240</v>
-      </c>
-      <c r="J21" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="K21" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="L21" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="M21" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="N21" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="O21" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="P21" s="16" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>241</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E22" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="F22" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="G22" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="H22" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="I22" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="P22" s="16" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>242</v>
-      </c>
-      <c r="D23" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="E23" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G23" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="H23" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="I23" s="16" t="s">
-        <v>236</v>
-      </c>
-      <c r="J23" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="K23" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="P23" s="16" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>243</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E24" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="F24" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G24" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="H24" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="I24" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="J24" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="K24" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="L24" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="M24" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="P24" s="16" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B25" s="16" t="s">
-        <v>244</v>
-      </c>
-      <c r="D25" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E25" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="F25" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G25" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="H25" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="I25" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="J25" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="K25" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="L25" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="M25" s="16" t="s">
-        <v>236</v>
-      </c>
-      <c r="P25" s="16" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B26" s="16" t="s">
-        <v>245</v>
-      </c>
-      <c r="D26" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="E26" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="F26" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="G26" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="H26" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="I26" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J26" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="K26" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="P26" s="16" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>246</v>
-      </c>
-      <c r="D27" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E27" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="F27" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G27" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="H27" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="I27" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="P27" s="16" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B28" s="16" t="s">
-        <v>247</v>
-      </c>
-      <c r="D28" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E28" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="F28" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="G28" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H28" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="I28" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="P28" s="16" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B29" s="16" t="s">
-        <v>248</v>
-      </c>
-      <c r="D29" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E29" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="F29" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G29" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="H29" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="I29" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J29" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="K29" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="P29" s="16" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B30" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="D30" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E30" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="F30" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="G30" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="H30" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="I30" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="J30" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="K30" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="P30" s="16" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B31" s="16" t="s">
-        <v>250</v>
-      </c>
-      <c r="D31" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E31" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="F31" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="G31" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="H31" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="I31" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="J31" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="K31" s="16" t="s">
-        <v>252</v>
-      </c>
-      <c r="P31" s="16" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>253</v>
-      </c>
-      <c r="D32" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E32" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="F32" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="G32" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="H32" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="I32" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="J32" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="K32" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="P32" s="16" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B33" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="D33" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E33" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="F33" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G33" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="H33" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="I33" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="J33" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="K33" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="P33" s="16" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B34" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="D34" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E34" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="F34" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="G34" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="H34" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="I34" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="J34" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="K34" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="L34" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="M34" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="P34" s="16" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B35" s="16" t="s">
-        <v>256</v>
-      </c>
-      <c r="D35" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E35" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="F35" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G35" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="H35" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="I35" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="J35" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="K35" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="P35" s="16" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B36" s="16" t="s">
-        <v>257</v>
-      </c>
-      <c r="D36" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E36" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="F36" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="G36" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="H36" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="I36" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="J36" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="K36" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="L36" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="M36" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="N36" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="O36" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="P36" s="16" t="s">
-        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -8822,1365 +8849,1382 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="17.25"/>
+    <col customWidth="1" min="3" max="3" width="20.88"/>
+    <col customWidth="1" min="4" max="4" width="17.13"/>
+  </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="B2" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="7" t="s">
-        <v>214</v>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="8" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="9" t="s">
+    </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="8" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="5" ht="22.5" customHeight="1">
+      <c r="A5" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F5" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="11" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="4" t="s">
+      <c r="G5" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="12" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="6" ht="22.5" customHeight="1">
+      <c r="A6" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="7" ht="22.5" customHeight="1">
+      <c r="A7" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="12" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="8" ht="22.5" customHeight="1">
+      <c r="A8" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="9" ht="22.5" customHeight="1">
+      <c r="A9" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="12" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="10" ht="22.5" customHeight="1">
+      <c r="A10" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="11" ht="22.5" customHeight="1">
+      <c r="A11" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="B11" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="12" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="12" ht="22.5" customHeight="1">
+      <c r="A12" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="H12" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B5" s="9" t="s">
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="8" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="13" ht="22.5" customHeight="1">
+      <c r="A13" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="12" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="14" ht="22.5" customHeight="1">
+      <c r="A14" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="E5" s="9" t="s">
+    </row>
+    <row r="15" ht="22.5" customHeight="1">
+      <c r="A15" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="E15" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F15" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="12" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="16" ht="22.5" customHeight="1">
+      <c r="A16" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="H5" s="9" t="s">
+      <c r="G16" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="17" ht="22.5" customHeight="1">
+      <c r="A17" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="12" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="18" ht="22.5" customHeight="1">
+      <c r="A18" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="19" ht="22.5" customHeight="1">
+      <c r="A19" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="12" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="20" ht="22.5" customHeight="1">
+      <c r="A20" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="8" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="21" ht="22.5" customHeight="1">
+      <c r="A21" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="12" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="22" ht="22.5" customHeight="1">
+      <c r="A22" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
+      <c r="O22" s="8" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="23" ht="22.5" customHeight="1">
+      <c r="A23" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="12" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="24" ht="22.5" customHeight="1">
+      <c r="A24" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+      <c r="O24" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="25" ht="22.5" customHeight="1">
+      <c r="A25" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="12" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="26" ht="22.5" customHeight="1">
+      <c r="A26" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
+      <c r="O26" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="27" ht="22.5" customHeight="1">
+      <c r="A27" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H27" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
+      <c r="O27" s="12" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="28" ht="22.5" customHeight="1">
+      <c r="A28" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K28" s="7"/>
+      <c r="L28" s="7"/>
+      <c r="M28" s="7"/>
+      <c r="N28" s="7"/>
+      <c r="O28" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="29" ht="22.5" customHeight="1">
+      <c r="A29" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J29" s="20" t="s">
+        <v>270</v>
+      </c>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
+      <c r="O29" s="12" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="30" ht="22.5" customHeight="1">
+      <c r="A30" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J30" s="20" t="s">
+        <v>270</v>
+      </c>
+      <c r="K30" s="7"/>
+      <c r="L30" s="7"/>
+      <c r="M30" s="7"/>
+      <c r="N30" s="7"/>
+      <c r="O30" s="8" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="31" ht="22.5" customHeight="1">
+      <c r="A31" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J31" s="20" t="s">
+        <v>270</v>
+      </c>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="11"/>
+      <c r="O31" s="12" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="32" ht="22.5" customHeight="1">
+      <c r="A32" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="M32" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="N32" s="20" t="s">
+        <v>270</v>
+      </c>
+      <c r="O32" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="33" ht="22.5" customHeight="1">
+      <c r="A33" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="K33" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="L33" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="M33" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="N33" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="O33" s="12" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="34" ht="22.5" customHeight="1">
+      <c r="A34" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="K34" s="7"/>
+      <c r="L34" s="7"/>
+      <c r="M34" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="N34" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="O34" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="35" ht="22.5" customHeight="1">
+      <c r="A35" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="K35" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="L35" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="M35" s="11"/>
+      <c r="N35" s="11"/>
+      <c r="O35" s="12" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="36" ht="22.5" customHeight="1">
+      <c r="A36" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B36" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="11" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="C36" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="G36" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="7" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H7" s="9" t="s">
+      <c r="H36" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J36" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="11" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="H8" s="5" t="s">
+      <c r="K36" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="L36" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="7" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="11" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="7" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="11" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="11" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="7" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="15" ht="22.5" customHeight="1">
-      <c r="A15" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="11" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="16" ht="22.5" customHeight="1">
-      <c r="A16" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="7" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="17" ht="22.5" customHeight="1">
-      <c r="A17" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-      <c r="O17" s="11" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="18" ht="22.5" customHeight="1">
-      <c r="A18" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="7" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="19" ht="22.5" customHeight="1">
-      <c r="A19" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
-      <c r="O19" s="11" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="20" ht="22.5" customHeight="1">
-      <c r="A20" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="6"/>
-      <c r="O20" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="21" ht="22.5" customHeight="1">
-      <c r="A21" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
-      <c r="O21" s="11" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="22" ht="22.5" customHeight="1">
-      <c r="A22" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
-      <c r="O22" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="23" ht="22.5" customHeight="1">
-      <c r="A23" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
-      <c r="O23" s="11" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="24" ht="22.5" customHeight="1">
-      <c r="A24" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="I24" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="6"/>
-      <c r="O24" s="7" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="25" ht="22.5" customHeight="1">
-      <c r="A25" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="J25" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="10"/>
-      <c r="O25" s="11" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="26" ht="22.5" customHeight="1">
-      <c r="A26" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="6"/>
-      <c r="N26" s="6"/>
-      <c r="O26" s="7" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="27" ht="22.5" customHeight="1">
-      <c r="A27" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="J27" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10"/>
-      <c r="M27" s="10"/>
-      <c r="N27" s="10"/>
-      <c r="O27" s="11" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="28" ht="22.5" customHeight="1">
-      <c r="A28" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J28" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="6"/>
-      <c r="N28" s="6"/>
-      <c r="O28" s="7" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="29" ht="22.5" customHeight="1">
-      <c r="A29" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
-      <c r="M29" s="10"/>
-      <c r="N29" s="10"/>
-      <c r="O29" s="11" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="30" ht="22.5" customHeight="1">
-      <c r="A30" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="6"/>
-      <c r="N30" s="6"/>
-      <c r="O30" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="31" ht="22.5" customHeight="1">
-      <c r="A31" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="10"/>
-      <c r="M31" s="10"/>
-      <c r="N31" s="10"/>
-      <c r="O31" s="11" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="32" ht="22.5" customHeight="1">
-      <c r="A32" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="I32" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J32" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K32" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="L32" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="M32" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="N32" s="5" t="s">
+      <c r="M36" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="N36" s="21" t="s">
         <v>270</v>
       </c>
-      <c r="O32" s="7" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="33" ht="22.5" customHeight="1">
-      <c r="A33" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="J33" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="K33" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="L33" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M33" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="N33" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="O33" s="11" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="34" ht="22.5" customHeight="1">
-      <c r="A34" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="H34" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="I34" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="J34" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="K34" s="6"/>
-      <c r="L34" s="6"/>
-      <c r="M34" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="N34" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="O34" s="7" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="35" ht="22.5" customHeight="1">
-      <c r="A35" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="J35" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="K35" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="L35" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="M35" s="10"/>
-      <c r="N35" s="10"/>
-      <c r="O35" s="11" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="36" ht="22.5" customHeight="1">
-      <c r="A36" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="I36" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="J36" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K36" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="L36" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="M36" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="N36" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="O36" s="7" t="s">
-        <v>230</v>
+      <c r="O36" s="8" t="s">
+        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -10248,7 +10292,7 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>102</v>
@@ -10256,48 +10300,48 @@
       <c r="D2" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="K2" s="22" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>44</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>51</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="K3" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="K3" s="22" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>150</v>
+        <v>278</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>86</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>44</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>110</v>
@@ -10305,13 +10349,13 @@
       <c r="H4" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="K4" s="17" t="s">
+      <c r="K4" s="22" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>102</v>
@@ -10331,13 +10375,13 @@
       <c r="H5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K5" s="17" t="s">
+      <c r="K5" s="22" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>77</v>
@@ -10355,15 +10399,15 @@
         <v>54</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="K6" s="17" t="s">
+        <v>283</v>
+      </c>
+      <c r="K6" s="22" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>57</v>
@@ -10383,13 +10427,13 @@
       <c r="H7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="K7" s="17" t="s">
+      <c r="K7" s="22" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>28</v>
@@ -10403,13 +10447,13 @@
       <c r="F8" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="K8" s="17" t="s">
+      <c r="K8" s="22" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>86</v>
@@ -10427,15 +10471,15 @@
         <v>51</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="K9" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="K9" s="22" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>77</v>
@@ -10447,7 +10491,7 @@
         <v>51</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>94</v>
@@ -10455,13 +10499,13 @@
       <c r="H10" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="K10" s="17" t="s">
+      <c r="K10" s="22" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>92</v>
@@ -10473,24 +10517,24 @@
         <v>19</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="K11" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="K11" s="22" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>154</v>
+        <v>292</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>21</v>
@@ -10510,33 +10554,33 @@
       <c r="H12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K12" s="17" t="s">
+      <c r="K12" s="22" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>89</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="K13" s="17" t="s">
+        <v>294</v>
+      </c>
+      <c r="K13" s="22" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>94</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>21</v>
@@ -10544,27 +10588,27 @@
       <c r="F14" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K14" s="17" t="s">
+      <c r="K14" s="22" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>63</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="K15" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="K15" s="22" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>140</v>
@@ -10578,13 +10622,13 @@
       <c r="F16" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="K16" s="17" t="s">
+      <c r="K16" s="22" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>104</v>
@@ -10598,13 +10642,13 @@
       <c r="F17" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="K17" s="17" t="s">
+      <c r="K17" s="22" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>72</v>
@@ -10618,13 +10662,13 @@
       <c r="F18" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K18" s="17" t="s">
+      <c r="K18" s="22" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>28</v>
@@ -10636,7 +10680,7 @@
         <v>32</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>160</v>
@@ -10644,13 +10688,13 @@
       <c r="H19" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K19" s="17" t="s">
+      <c r="K19" s="22" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>74</v>
@@ -10664,16 +10708,16 @@
       <c r="F20" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K20" s="17" t="s">
+      <c r="K20" s="22" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>126</v>
@@ -10685,21 +10729,21 @@
         <v>74</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>304</v>
+        <v>168</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>120</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="K21" s="17" t="s">
+        <v>307</v>
+      </c>
+      <c r="K21" s="22" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>120</v>
@@ -10713,16 +10757,16 @@
       <c r="F22" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K22" s="17" t="s">
+      <c r="K22" s="22" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>126</v>
@@ -10734,15 +10778,15 @@
         <v>120</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="K23" s="17" t="s">
+        <v>310</v>
+      </c>
+      <c r="K23" s="22" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>81</v>
@@ -10756,16 +10800,16 @@
       <c r="F24" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="K24" s="17" t="s">
+      <c r="K24" s="22" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>81</v>
@@ -10779,13 +10823,13 @@
       <c r="F25" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="K25" s="17" t="s">
+      <c r="K25" s="22" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>98</v>
@@ -10799,13 +10843,13 @@
       <c r="F26" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K26" s="17" t="s">
+      <c r="K26" s="22" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>19</v>
@@ -10819,16 +10863,16 @@
       <c r="F27" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="K27" s="17" t="s">
+      <c r="K27" s="22" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>154</v>
+        <v>292</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>21</v>
@@ -10840,7 +10884,7 @@
         <v>54</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>51</v>
@@ -10848,19 +10892,19 @@
       <c r="H28" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="K28" s="17" t="s">
+      <c r="K28" s="22" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>51</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>54</v>
@@ -10874,30 +10918,30 @@
       <c r="H29" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K29" s="17" t="s">
+      <c r="K29" s="22" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="K30" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="K30" s="22" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="31" ht="22.5" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>154</v>
+        <v>292</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>21</v>
@@ -10911,13 +10955,13 @@
       <c r="F31" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="K31" s="17" t="s">
+      <c r="K31" s="22" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="32" ht="22.5" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>81</v>
@@ -10935,7 +10979,7 @@
         <v>72</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>110</v>
@@ -10943,13 +10987,13 @@
       <c r="J32" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="K32" s="17" t="s">
+      <c r="K32" s="22" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="33" ht="22.5" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>89</v>
@@ -10963,13 +11007,13 @@
       <c r="F33" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="K33" s="17" t="s">
+      <c r="K33" s="22" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="34" ht="22.5" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>44</v>
@@ -10983,47 +11027,47 @@
       <c r="F34" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K34" s="17" t="s">
+      <c r="K34" s="22" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="35" ht="22.5" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>120</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="K35" s="17" t="s">
+        <v>328</v>
+      </c>
+      <c r="K35" s="22" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="36" ht="22.5" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="K36" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="K36" s="22" t="s">
         <v>30</v>
       </c>
     </row>
@@ -11051,176 +11095,176 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="K1" s="18" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="s">
-        <v>329</v>
-      </c>
-      <c r="C2" s="16" t="s">
+      <c r="A2" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="C2" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="D2" s="16" t="s">
-        <v>330</v>
-      </c>
-      <c r="K2" s="16" t="s">
+      <c r="D2" s="18" t="s">
+        <v>332</v>
+      </c>
+      <c r="K2" s="18" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="s">
-        <v>331</v>
-      </c>
-      <c r="C3" s="16" t="s">
+      <c r="A3" s="18" t="s">
+        <v>333</v>
+      </c>
+      <c r="C3" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="D3" s="16" t="s">
-        <v>330</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="16" t="s">
+      <c r="D3" s="18" t="s">
         <v>332</v>
       </c>
-      <c r="K3" s="16" t="s">
+      <c r="E3" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>334</v>
+      </c>
+      <c r="K3" s="18" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="s">
-        <v>333</v>
-      </c>
-      <c r="C4" s="16" t="s">
+      <c r="A4" s="18" t="s">
+        <v>335</v>
+      </c>
+      <c r="C4" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="D4" s="16" t="s">
-        <v>330</v>
-      </c>
-      <c r="E4" s="16" t="s">
+      <c r="D4" s="18" t="s">
+        <v>332</v>
+      </c>
+      <c r="E4" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="F4" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="K4" s="16" t="s">
+      <c r="F4" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="K4" s="18" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="s">
-        <v>334</v>
-      </c>
-      <c r="C5" s="16" t="s">
+      <c r="A5" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="C5" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="D5" s="16" t="s">
-        <v>335</v>
-      </c>
-      <c r="E5" s="16" t="s">
+      <c r="D5" s="18" t="s">
+        <v>337</v>
+      </c>
+      <c r="E5" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="H5" s="16" t="s">
-        <v>336</v>
-      </c>
-      <c r="I5" s="16" t="s">
+      <c r="H5" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="I5" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="J5" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="K5" s="16" t="s">
+      <c r="K5" s="18" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="s">
+        <v>340</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" s="18" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="16" t="s">
-        <v>338</v>
-      </c>
-      <c r="C6" s="16" t="s">
+      <c r="E6" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>341</v>
+      </c>
+      <c r="K6" s="18" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="s">
+        <v>342</v>
+      </c>
+      <c r="C7" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="D6" s="16" t="s">
-        <v>335</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="H6" s="16" t="s">
+      <c r="D7" s="18" t="s">
+        <v>337</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="K7" s="18" t="s">
         <v>339</v>
-      </c>
-      <c r="K6" s="16" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="s">
-        <v>340</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>335</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="K7" s="16" t="s">
-        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -11248,31 +11292,31 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
@@ -11280,21 +11324,21 @@
         <v>101</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>350</v>
-      </c>
-      <c r="D2" s="18">
+        <v>351</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="D2" s="23">
         <v>1.0</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>104</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="I2" s="18">
+        <v>353</v>
+      </c>
+      <c r="I2" s="23">
         <v>3.0</v>
       </c>
     </row>
@@ -11305,19 +11349,19 @@
       <c r="B3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="17" t="s">
-        <v>350</v>
-      </c>
-      <c r="D3" s="18">
+      <c r="C3" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="D3" s="23">
         <v>1.0</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="I3" s="18">
+        <v>354</v>
+      </c>
+      <c r="I3" s="23">
         <v>1.0</v>
       </c>
     </row>
@@ -11326,21 +11370,21 @@
         <v>80</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>350</v>
-      </c>
-      <c r="D4" s="18">
+        <v>355</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="D4" s="23">
         <v>1.0</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>81</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="I4" s="18">
+        <v>356</v>
+      </c>
+      <c r="I4" s="23">
         <v>1.0</v>
       </c>
     </row>
@@ -11349,21 +11393,21 @@
         <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>350</v>
-      </c>
-      <c r="D5" s="18">
+        <v>357</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="D5" s="23">
         <v>1.0</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>44</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="I5" s="18">
+        <v>358</v>
+      </c>
+      <c r="I5" s="23">
         <v>1.0</v>
       </c>
     </row>
@@ -11372,35 +11416,35 @@
         <v>137</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>350</v>
-      </c>
-      <c r="D6" s="18">
+        <v>359</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="D6" s="23">
         <v>1.0</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="24">
         <v>46024.0</v>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="23">
         <v>3.0</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>350</v>
-      </c>
-      <c r="D7" s="20"/>
+        <v>361</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="D7" s="25"/>
       <c r="F7" s="2">
         <v>2.0</v>
       </c>
@@ -11410,7 +11454,7 @@
       <c r="H7" s="2">
         <v>12.0</v>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="23">
         <v>1.0</v>
       </c>
     </row>
@@ -11421,33 +11465,33 @@
       <c r="B8" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C8" s="17" t="s">
-        <v>350</v>
-      </c>
-      <c r="D8" s="18">
+      <c r="C8" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="D8" s="23">
         <v>1.0</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>140</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="I8" s="18">
+        <v>362</v>
+      </c>
+      <c r="I8" s="23">
         <v>3.0</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>350</v>
-      </c>
-      <c r="D9" s="18">
+        <v>363</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="D9" s="23">
         <v>1.0</v>
       </c>
       <c r="G9" s="2" t="s">
@@ -11456,7 +11500,7 @@
       <c r="H9" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="23">
         <v>3.0</v>
       </c>
     </row>
@@ -11467,10 +11511,10 @@
       <c r="B10" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C10" s="17" t="s">
-        <v>350</v>
-      </c>
-      <c r="D10" s="18">
+      <c r="C10" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="D10" s="23">
         <v>1.0</v>
       </c>
       <c r="G10" s="2" t="s">
@@ -11479,7 +11523,7 @@
       <c r="H10" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="I10" s="18">
+      <c r="I10" s="23">
         <v>3.0</v>
       </c>
     </row>
@@ -11490,10 +11534,10 @@
       <c r="B11" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C11" s="17" t="s">
-        <v>350</v>
-      </c>
-      <c r="D11" s="18">
+      <c r="C11" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="D11" s="23">
         <v>1.0</v>
       </c>
       <c r="G11" s="2" t="s">
@@ -11502,7 +11546,7 @@
       <c r="H11" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="23">
         <v>3.0</v>
       </c>
     </row>
@@ -11513,10 +11557,10 @@
       <c r="B12" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C12" s="17" t="s">
-        <v>350</v>
-      </c>
-      <c r="D12" s="20"/>
+      <c r="C12" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="D12" s="25"/>
       <c r="E12" s="2">
         <v>2.0</v>
       </c>
@@ -11527,23 +11571,23 @@
         <v>74</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="I12" s="18">
+        <v>364</v>
+      </c>
+      <c r="I12" s="23">
         <v>1.0</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>364</v>
-      </c>
-      <c r="D13" s="20"/>
+        <v>365</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>366</v>
+      </c>
+      <c r="D13" s="25"/>
       <c r="E13" s="2">
         <v>4.0</v>
       </c>
@@ -11551,90 +11595,90 @@
         <v>1.0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H13" s="2">
         <v>1.0</v>
       </c>
-      <c r="I13" s="20"/>
+      <c r="I13" s="25"/>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C14" s="22" t="s">
         <v>366</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>364</v>
-      </c>
-      <c r="D14" s="18">
+      <c r="D14" s="23">
         <v>1.0</v>
       </c>
       <c r="F14" s="2">
         <v>3.0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H14" s="2">
         <v>10.0</v>
       </c>
-      <c r="I14" s="20"/>
+      <c r="I14" s="25"/>
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>154</v>
+        <v>292</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>364</v>
-      </c>
-      <c r="D15" s="18">
+        <v>370</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>366</v>
+      </c>
+      <c r="D15" s="23">
         <v>1.0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H15" s="2">
         <v>3.0</v>
       </c>
-      <c r="I15" s="20"/>
+      <c r="I15" s="25"/>
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>366</v>
+      </c>
+      <c r="D16" s="23">
+        <v>1.0</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>371</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>364</v>
-      </c>
-      <c r="D16" s="18">
-        <v>1.0</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>369</v>
       </c>
       <c r="H16" s="2">
         <v>4.0</v>
       </c>
-      <c r="I16" s="20"/>
+      <c r="I16" s="25"/>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>364</v>
-      </c>
-      <c r="D17" s="20"/>
+        <v>374</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>366</v>
+      </c>
+      <c r="D17" s="25"/>
       <c r="E17" s="2">
         <v>6.0</v>
       </c>
@@ -11642,76 +11686,76 @@
         <v>2.0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H17" s="2">
         <v>2.0</v>
       </c>
-      <c r="I17" s="20"/>
+      <c r="I17" s="25"/>
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>364</v>
-      </c>
-      <c r="D18" s="18">
+        <v>375</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>366</v>
+      </c>
+      <c r="D18" s="23">
         <v>1.0</v>
       </c>
       <c r="F18" s="2">
         <v>3.0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H18" s="2">
         <v>14.0</v>
       </c>
-      <c r="I18" s="20"/>
+      <c r="I18" s="25"/>
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>375</v>
-      </c>
-      <c r="D19" s="18">
+        <v>376</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>377</v>
+      </c>
+      <c r="D19" s="23">
         <v>2.0</v>
       </c>
       <c r="E19" s="2">
         <v>8.0</v>
       </c>
-      <c r="I19" s="20"/>
+      <c r="I19" s="25"/>
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>375</v>
-      </c>
-      <c r="D20" s="18">
+        <v>278</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>377</v>
+      </c>
+      <c r="D20" s="23">
         <v>2.0</v>
       </c>
-      <c r="I20" s="20"/>
+      <c r="I20" s="25"/>
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>375</v>
-      </c>
-      <c r="D21" s="20"/>
+        <v>378</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>377</v>
+      </c>
+      <c r="D21" s="25"/>
       <c r="E21" s="2">
         <v>4.0</v>
       </c>
-      <c r="I21" s="20"/>
+      <c r="I21" s="25"/>
     </row>
   </sheetData>
   <dataValidations>
